--- a/data/trans_orig/Q5417-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82327</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66267</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86761</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95002</t>
+          <t>94928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>245161</t>
+          <t>244774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256307</t>
+          <t>256198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327587</t>
+          <t>327837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340203</t>
+          <t>340237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80516</t>
+          <t>81877</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92689</t>
+          <t>92974</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>133878</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>147294</t>
+          <t>146656</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>396013</t>
+          <t>396030</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>413010</t>
+          <t>413157</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>399644</t>
+          <t>399052</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>417073</t>
+          <t>417258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>47040</t>
+          <t>46013</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>482373</t>
+          <t>482305</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>495210</t>
+          <t>495244</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>630461</t>
+          <t>629853</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>653490</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1118340</t>
+          <t>1118184</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1144818</t>
+          <t>1144253</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63620</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110143</t>
+          <t>110241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117686</t>
+          <t>117691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164810</t>
+          <t>164516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172302</t>
+          <t>172294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205905</t>
+          <t>206798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223295</t>
+          <t>223246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264632</t>
+          <t>264553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282233</t>
+          <t>282349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>89599</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100608</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>149321</t>
+          <t>149490</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>169798</t>
+          <t>169069</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>243505</t>
+          <t>243404</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>266976</t>
+          <t>266221</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,47 +8071,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>14709</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>23579</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>5,94%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>14709</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>23244</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>350568</t>
+          <t>350394</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>373098</t>
+          <t>374320</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>353058</t>
+          <t>353940</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375257</t>
+          <t>376292</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>50511</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69112</t>
+          <t>69061</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>521570</t>
+          <t>522689</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>542817</t>
+          <t>542791</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>657731</t>
+          <t>659126</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>691424</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1185924</t>
+          <t>1187831</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1225890</t>
+          <t>1227254</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95258</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>52478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63053</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70079</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111582</t>
+          <t>111481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119476</t>
+          <t>119487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154471</t>
+          <t>154738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164642</t>
+          <t>164593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191992</t>
+          <t>191492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200580</t>
+          <t>201338</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89509</t>
+          <t>88532</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97800</t>
+          <t>97777</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284928</t>
+          <t>284191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>297701</t>
+          <t>297384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>134229</t>
+          <t>133402</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142721</t>
+          <t>142774</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>137368</t>
+          <t>135980</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>153127</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>275612</t>
+          <t>275770</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>293738</t>
+          <t>293542</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17311</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>372928</t>
+          <t>373754</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>396337</t>
+          <t>396196</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>372928</t>
+          <t>373754</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>396337</t>
+          <t>396196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>45243</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29522</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>57465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>562398</t>
+          <t>562283</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>578675</t>
+          <t>578740</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>709752</t>
+          <t>708843</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>739760</t>
+          <t>738646</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1280918</t>
+          <t>1278156</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1312893</t>
+          <t>1312230</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>62190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169855</t>
+          <t>169875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91908</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>42421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136379</t>
+          <t>136383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141005</t>
+          <t>141003</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94565</t>
+          <t>94079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100934</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49070</t>
+          <t>48575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>145627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152696</t>
+          <t>152655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>221913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231862</t>
+          <t>231884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310253</t>
+          <t>309904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>325901</t>
+          <t>325866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>536688</t>
+          <t>536731</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559194</t>
+          <t>559553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -15886,12 +15886,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91100</t>
+          <t>91166</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>178898</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>191040</t>
+          <t>191111</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>267995</t>
+          <t>268278</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>281034</t>
+          <t>280666</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>283877</t>
+          <t>284755</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>299991</t>
+          <t>300156</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>288872</t>
+          <t>287541</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>613256</t>
+          <t>613201</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>626171</t>
+          <t>626230</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>941436</t>
+          <t>943504</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>986074</t>
+          <t>989702</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1563923</t>
+          <t>1564131</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1607068</t>
+          <t>1607546</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5417-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Clase-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82901</t>
+          <t>84039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>61574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>66159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87068</t>
+          <t>86570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94928</t>
+          <t>95013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244774</t>
+          <t>244418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256198</t>
+          <t>256373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>79068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327837</t>
+          <t>327496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340237</t>
+          <t>340207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49178</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81877</t>
+          <t>81130</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92974</t>
+          <t>92853</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>133578</t>
+          <t>133966</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>147159</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>396030</t>
+          <t>395798</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>413157</t>
+          <t>414082</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>399052</t>
+          <t>399201</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>417258</t>
+          <t>417220</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>45972</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>482305</t>
+          <t>481220</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>495244</t>
+          <t>494449</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>629853</t>
+          <t>630344</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>653390</t>
+          <t>652980</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1118184</t>
+          <t>1117615</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1144253</t>
+          <t>1145149</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63701</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>68068</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77419</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110241</t>
+          <t>109789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117691</t>
+          <t>117689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164516</t>
+          <t>164513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172294</t>
+          <t>172289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>206798</t>
+          <t>207011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223246</t>
+          <t>222516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264553</t>
+          <t>264876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282349</t>
+          <t>282357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,47 +7276,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>7624</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>14925</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>7624</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3285</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>15601</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,47 +7374,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>4397</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>1068</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>4397</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>29618</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89599</t>
+          <t>90303</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>100612</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>149490</t>
+          <t>148885</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>169069</t>
+          <t>168726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>243404</t>
+          <t>244610</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>266221</t>
+          <t>267027</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>350394</t>
+          <t>352283</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>374320</t>
+          <t>373215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>353940</t>
+          <t>353303</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>376292</t>
+          <t>375421</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8497,77 +8497,77 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>14023</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>23706</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>18376</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>10641</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>30440</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>14023</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>7574</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>24292</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>18376</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>10865</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>31373</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26803</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>50820</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>67564</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>520565</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>542791</t>
+          <t>541850</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>659126</t>
+          <t>659603</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>691424</t>
+          <t>690844</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1187831</t>
+          <t>1188637</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1227254</t>
+          <t>1226111</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>46637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52478</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>63127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>70051</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111481</t>
+          <t>111546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119487</t>
+          <t>119478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154738</t>
+          <t>155552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164593</t>
+          <t>164710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>16021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191492</t>
+          <t>191440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201338</t>
+          <t>200651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>88508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284191</t>
+          <t>284580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>297384</t>
+          <t>297509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>800</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133402</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142774</t>
+          <t>142674</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>135980</t>
+          <t>137883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153127</t>
+          <t>153308</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>275770</t>
+          <t>275655</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>293542</t>
+          <t>293563</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>373754</t>
+          <t>373772</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>396196</t>
+          <t>396799</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>373754</t>
+          <t>373772</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>396196</t>
+          <t>396799</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,42 +12601,42 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>19288</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>3693</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>17810</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12749,42 +12749,42 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>11538</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>6361</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>20712</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>11538</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>6036</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>20610</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>30716</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>58244</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>562283</t>
+          <t>561678</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>578740</t>
+          <t>578810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>708843</t>
+          <t>708671</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>738646</t>
+          <t>739551</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1278156</t>
+          <t>1278261</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1312230</t>
+          <t>1312356</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>897</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -13650,57 +13650,57 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3025</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -13753,62 +13753,62 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>73662</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>71515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>194063</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>192189</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>194960</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>98,58%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>171975</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>169875</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>172900</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>581</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>581</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14028,12 +14028,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>398</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -14287,27 +14287,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>104117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91928</t>
+          <t>101139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>53404</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46198</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>139436</t>
+          <t>157521</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136383</t>
+          <t>154089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141003</t>
+          <t>159169</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -14743,32 +14743,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98473</t>
+          <t>108825</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94079</t>
+          <t>104650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,27 +14891,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48575</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>165391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145627</t>
+          <t>160707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152655</t>
+          <t>168401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>313</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -15131,12 +15131,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>655</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>227528</t>
+          <t>248479</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221913</t>
+          <t>241115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231884</t>
+          <t>252949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>321479</t>
+          <t>125507</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>309904</t>
+          <t>121233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>325866</t>
+          <t>128181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>549007</t>
+          <t>373987</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>536731</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559553</t>
+          <t>379509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>237674</t>
+          <t>259504</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237674</t>
+          <t>259504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237674</t>
+          <t>259504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>564368</t>
+          <t>390384</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>564368</t>
+          <t>390384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>564368</t>
+          <t>390384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -15665,12 +15665,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,17 +15690,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -15881,22 +15881,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,32 +15916,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>98041</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85804</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91166</t>
+          <t>99635</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185717</t>
+          <t>199208</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>179298</t>
+          <t>192003</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>191111</t>
+          <t>204675</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>275048</t>
+          <t>297249</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>268278</t>
+          <t>288944</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>280666</t>
+          <t>302805</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16259,67 +16259,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>11569</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>3161</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>11291</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -16485,32 +16485,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16520,32 +16520,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -16598,67 +16598,67 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>293425</t>
+          <t>315192</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>284755</t>
+          <t>305331</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>300156</t>
+          <t>322797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>318468</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>308992</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>326120</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>88,52%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>93,31%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>296629</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>287541</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>303684</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>91,31%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>88,51%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -16906,102 +16906,102 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>8188</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>13615</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>18591</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>7383</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>12262</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>10303</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>5719</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>16812</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>50419</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>49972</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>42881</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>63532</t>
+          <t>67176</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>620501</t>
+          <t>683141</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>613201</t>
+          <t>675099</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>626230</t>
+          <t>689074</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>961649</t>
+          <t>823539</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>943504</t>
+          <t>811941</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>989702</t>
+          <t>834362</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1582150</t>
+          <t>1506680</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1564131</t>
+          <t>1492470</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1607546</t>
+          <t>1519727</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>637530</t>
+          <t>701161</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>637530</t>
+          <t>701161</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>637530</t>
+          <t>701161</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1018192</t>
+          <t>884476</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1018192</t>
+          <t>884476</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1018192</t>
+          <t>884476</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1655722</t>
+          <t>1585637</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1655722</t>
+          <t>1585637</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1655722</t>
+          <t>1585637</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
